--- a/fuction_ensemble/redes-ensemble-s/mse_sup_ensemble_100/content/results/metrics_11_9.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/mse_sup_ensemble_100/content/results/metrics_11_9.xlsx
@@ -517,657 +517,657 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9973270572211722</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7519460636048646</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9309267450719702</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9908741935015244</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9881931489117882</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01787398066979142</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.658737814857624</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006633137945402345</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01568876179248804</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01116094986894519</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1407175994391248</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1336936074380201</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N2" t="n">
-        <v>1.002566025067675</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1393852210905766</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P2" t="n">
-        <v>106.0488184349886</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q2" t="n">
-        <v>165.7737338535304</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_1</t>
+          <t>model_11_9_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9975523461929763</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7517183118010852</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8680660817237642</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9899556406892852</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9841649263943367</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01636747227797699</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.660260792218197</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01266967772860205</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01726790510080248</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01496880593847077</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1785259451540186</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1279354222956918</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N3" t="n">
-        <v>1.002349747654743</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O3" t="n">
-        <v>0.133381898085653</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P3" t="n">
-        <v>106.2249186227484</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q3" t="n">
-        <v>165.9498340412902</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_2</t>
+          <t>model_11_9_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9976695681924395</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7514585772260393</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7922540347846547</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9890239210121675</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9794669332203009</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01558360822780913</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.661997638517497</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0199499451171071</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01886968441467634</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.019409792439301</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2125874389868418</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1248343231159168</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N4" t="n">
-        <v>1.002237214535258</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1301487786936347</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P4" t="n">
-        <v>106.3230713435678</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q4" t="n">
-        <v>166.0479867621097</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_3</t>
+          <t>model_11_9_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9977065311808513</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7511813772596548</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D5" t="n">
-        <v>0.70880784615585</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E5" t="n">
-        <v>0.988095839584413</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9743844577648535</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0153364365541006</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.663851275969098</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02796332280966916</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02046520897971105</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02421422787636916</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2432492190147618</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1238403672236989</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N5" t="n">
-        <v>1.002201730066383</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1291125080413127</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P5" t="n">
-        <v>106.3550476153499</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q5" t="n">
-        <v>166.0799630338917</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_4</t>
+          <t>model_11_9_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9976848592549783</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7508973356292044</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6216842516895758</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E6" t="n">
-        <v>0.987184657358811</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9691305188036933</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01548135682220333</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.665750663659812</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03632984355632038</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02203168103775968</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02918074680016194</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2708321321990829</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1244241006485614</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N6" t="n">
-        <v>1.002222535115221</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1297210922065664</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P6" t="n">
-        <v>106.3362375292969</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q6" t="n">
-        <v>166.0611529478387</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_5</t>
+          <t>model_11_9_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9976213537768894</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7506141459883928</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D7" t="n">
-        <v>0.533776395849494</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9863006833616222</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F7" t="n">
-        <v>0.963861476058592</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01590601824659951</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.667644354091887</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04477167730050061</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02355137767771851</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03416154324588997</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2956385625861323</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1261190637714993</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N7" t="n">
-        <v>1.002283500374186</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1314882134187051</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P7" t="n">
-        <v>106.2821154705917</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q7" t="n">
-        <v>166.0070308891335</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_6</t>
+          <t>model_11_9_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9975289809737491</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7503372919183323</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4471753201723302</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9854515311276673</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9586905412864013</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01652371560653604</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.669495678533177</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05308802031612053</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02501120998145009</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03904959877710835</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.317935098066816</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1285446055131682</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N8" t="n">
-        <v>1.002372178265201</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1340170154938805</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P8" t="n">
-        <v>106.2059172410583</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q8" t="n">
-        <v>165.9308326596001</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_7</t>
+          <t>model_11_9_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9974176115160976</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C9" t="n">
-        <v>0.750070572210263</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3633145188515164</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9846428067433042</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9536955156503905</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01726844368266092</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.671279234449169</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06114121346522761</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02640154016477899</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04377136839214775</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3379743875882694</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1314094505074156</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N9" t="n">
-        <v>1.002479092944546</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1370038228705797</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P9" t="n">
-        <v>106.1177490153921</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q9" t="n">
-        <v>165.842664433934</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_8</t>
+          <t>model_11_9_15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9972947705590128</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7498165167940691</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2831751997381579</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9838774652631189</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F10" t="n">
-        <v>0.948929019598474</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01808988172831706</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>1.672978104187074</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0688370308852029</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.02771728800301582</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.04827711027781272</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3559860376745864</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1344986309533188</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N10" t="n">
-        <v>1.002597020263348</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1402245161235501</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P10" t="n">
-        <v>106.0248050351111</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q10" t="n">
-        <v>165.7497204536529</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_9</t>
+          <t>model_11_9_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9971660656318477</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7495765733405436</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2073500335749482</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9831578911282466</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9444231975103351</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01895053216890198</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>1.674582607165638</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07611855811911822</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02895435424981089</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.05253643853294026</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3721678102890041</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1376609318902861</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N11" t="n">
-        <v>1.002720576993426</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1435214427582694</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P11" t="n">
-        <v>105.9318465301127</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q11" t="n">
-        <v>165.6567619486545</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_10</t>
+          <t>model_11_9_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9970356822406212</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7493515903338013</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1361772130166595</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9824850375234064</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9401961411955442</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01982240650639416</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>1.676087069567675</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08295331836341821</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.03011110022391392</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.05653225107178837</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3867135095570123</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1407920683362318</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N12" t="n">
-        <v>1.002845745049004</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O12" t="n">
-        <v>0.146785878165065</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P12" t="n">
-        <v>105.8418846787368</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q12" t="n">
-        <v>165.5668000972787</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_11</t>
+          <t>model_11_9_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9969066856402471</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C13" t="n">
-        <v>0.749141868176069</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0698130957578893</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9818586667806769</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9362557131571738</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G13" t="n">
-        <v>0.02068500736707031</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>1.677489482602113</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08932629651336849</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.03118793451555804</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>0.06025711551446326</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3997819335306487</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1438228332604747</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N13" t="n">
-        <v>1.002969581785363</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1499456690266812</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P13" t="n">
-        <v>105.7566922458273</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q13" t="n">
-        <v>165.4816076643691</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="14">
@@ -1177,657 +1177,657 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9967811881922388</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7489472822973386</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D14" t="n">
-        <v>0.008245536870238657</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9812773301846206</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9325998001095401</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G14" t="n">
-        <v>0.02152420937976458</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>1.678790679269168</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I14" t="n">
-        <v>0.09523865885229378</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.03218734770477099</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.06371302953802553</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4115255728648723</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1467113130599157</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N14" t="n">
-        <v>1.003090059335451</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1529571173911619</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P14" t="n">
-        <v>105.6771539193349</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q14" t="n">
-        <v>165.4020693378767</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_13</t>
+          <t>model_11_9_10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9966607068629058</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7487675110122379</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.04863251133413904</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9807402544263994</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9292223709470051</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G15" t="n">
-        <v>0.02232986858377993</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>1.679992810680407</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1007006852212261</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.03311066923658948</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>0.06690569431268359</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4220812099032159</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1494318191811233</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N15" t="n">
-        <v>1.003205721411611</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1557934410901734</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P15" t="n">
-        <v>105.6036601966683</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q15" t="n">
-        <v>165.3285756152101</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_14</t>
+          <t>model_11_9_9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9965461908340532</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7486018934712719</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1009885858894677</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9802450405272951</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9261127052231752</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G16" t="n">
-        <v>0.02309563779601557</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>1.681100295939446</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1057284642822695</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.03396202334985895</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.06984524381606423</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4315698773916754</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1519724902606244</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N16" t="n">
-        <v>1.003315656799309</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O16" t="n">
-        <v>0.158442273797443</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P16" t="n">
-        <v>105.5362230385725</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q16" t="n">
-        <v>165.2611384571143</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_15</t>
+          <t>model_11_9_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9964382522373721</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7484498329745584</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1490346580945727</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9797898086540591</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9232582798999442</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G17" t="n">
-        <v>0.02381742368903261</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>1.682117125181143</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1103423517413633</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.03474464178700651</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>0.07254351600559297</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4400975534507659</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1543289463744006</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N17" t="n">
-        <v>1.003419277852123</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1608990491265193</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P17" t="n">
-        <v>105.4746757567515</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q17" t="n">
-        <v>165.1995911752934</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_16</t>
+          <t>model_11_9_7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9963371622145991</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7483105121997549</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1930206513511803</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9793722319756599</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9206443636646982</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G18" t="n">
-        <v>0.02449341313679284</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>1.683048763843767</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1145663478631707</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03546252475314172</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.07501443630815623</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4477664680736909</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1565037160478717</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N18" t="n">
-        <v>1.003516324273985</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1631664032473839</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P18" t="n">
-        <v>105.418702098276</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q18" t="n">
-        <v>165.1436175168178</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_17</t>
+          <t>model_11_9_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9962430496524863</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7481831757780411</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2331880113030267</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9789902616443122</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9182567683994466</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G19" t="n">
-        <v>0.02512274427298926</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>1.683900263082098</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1184236387891715</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.03611919455446976</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>0.07727141667182064</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4546569461846428</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1585015592131171</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N19" t="n">
-        <v>1.003606672333613</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1652492987322792</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P19" t="n">
-        <v>105.3679633936258</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q19" t="n">
-        <v>165.0928788121676</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_18</t>
+          <t>model_11_9_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9961557931720955</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7480669677104411</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2698117793707626</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9786412139855428</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9160790851709124</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G20" t="n">
-        <v>0.02570622875914233</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>1.684677346965227</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1219406368794864</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.03671926486864675</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>0.07932996836884162</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4608537713798683</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1603316212078651</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N20" t="n">
-        <v>1.003690438554788</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1671572702548942</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P20" t="n">
-        <v>105.3220439045549</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q20" t="n">
-        <v>165.0469593230967</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_19</t>
+          <t>model_11_9_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9960752071649054</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7479610929854805</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3031551619390549</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9783230664645</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9140961146358095</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02624510776028701</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>1.685385331738548</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1251426179700294</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.03726621276561847</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0812044592528653</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4664248367501875</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1620034189771531</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N21" t="n">
-        <v>1.003767801121691</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1689002399163193</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P21" t="n">
-        <v>105.2805513567009</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q21" t="n">
-        <v>165.0054667752427</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_20</t>
+          <t>model_11_9_3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.996001012734625</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7478647616531158</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3334648752256228</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9780330206051988</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9122929084887972</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02674124625720558</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>1.686029499801635</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1280532743380387</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.03776484928571493</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.08290901987278143</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4714349237200956</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1635275091756906</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N22" t="n">
-        <v>1.00383902777476</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1704892137899102</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P22" t="n">
-        <v>105.243096203834</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q22" t="n">
-        <v>164.9680116223758</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_21</t>
+          <t>model_11_9_2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9959328970448492</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7477772305945413</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.360985888718766</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9777690543775426</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F23" t="n">
-        <v>0.910654941826184</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0271967361883807</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>1.686614820393367</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1306961305214848</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.03821865063112495</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.08445738053828356</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4759435865796228</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1649143298454707</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N23" t="n">
-        <v>1.003904418836945</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1719350742867174</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P23" t="n">
-        <v>105.2093166119083</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q23" t="n">
-        <v>164.9342320304502</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_22</t>
+          <t>model_11_9_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9958704977505393</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7476978105801819</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.385957848800131</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9775292555316417</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9091684214731227</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G24" t="n">
-        <v>0.02761400055675348</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>1.687145902395083</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1330941998778423</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.03863090427381194</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.08586257985990872</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4799964335321423</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1661746086402898</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N24" t="n">
-        <v>1.003964322159482</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1732490057589687</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P24" t="n">
-        <v>105.1788647366524</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q24" t="n">
-        <v>164.9037801551942</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_11_9_23</t>
+          <t>model_11_9_11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9958135101551847</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7476257283089139</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4085744167881551</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9773118552723731</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9078219457171185</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G25" t="n">
-        <v>0.02799507686929275</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>1.68762791687496</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I25" t="n">
-        <v>0.135266079796813</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0390046510634092</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.08713539581229397</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4836390726964878</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1673172939934565</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N25" t="n">
-        <v>1.004019030251023</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1744403375933045</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P25" t="n">
-        <v>105.1514532207257</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q25" t="n">
-        <v>164.8763686392675</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9957614977691549</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7475604420415364</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4290539643443663</v>
+        <v>0.9999807865967625</v>
       </c>
       <c r="E26" t="n">
-        <v>0.977114209781437</v>
+        <v>0.9999096481882666</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9066020161271953</v>
+        <v>0.9999517488636962</v>
       </c>
       <c r="G26" t="n">
-        <v>0.02834288393416972</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>1.68806448644553</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1372327406142498</v>
+        <v>1.424621400004355e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.03934443615825786</v>
+        <v>4.650930515374975e-05</v>
       </c>
       <c r="K26" t="n">
-        <v>0.08828858838625381</v>
+        <v>3.037775957689665e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4869189266406067</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1683534494275948</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N26" t="n">
-        <v>1.004068962141611</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1755206043094115</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P26" t="n">
-        <v>105.1267585758582</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q26" t="n">
-        <v>164.8516739944001</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
   </sheetData>
